--- a/Agile Documents/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/Agile Documents/Unit_Test_Plan_v0.1 (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ccdc670acfc4ce0/Desktop/.tmp.driveupload/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ai_Project_Intelligence_Risk_Advisor\Agile Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E8276C0-1E27-4C03-8729-C845936D6F72}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB2EE7C-769A-4A67-B113-C958615B14A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t>Actual Result</t>
   </si>
@@ -465,6 +465,156 @@
   </si>
   <si>
     <t>Scope, risk and blocker results were displayed successfully in the Streamlit dashboard.</t>
+  </si>
+  <si>
+    <t>Documentation Agent – User Story Generation</t>
+  </si>
+  <si>
+    <t>Upload a valid project document and run the Documentation Generation Agent</t>
+  </si>
+  <si>
+    <t>Project document contains project objectives, requirements, features or deliverables</t>
+  </si>
+  <si>
+    <t>User stories are generated based on the uploaded project content</t>
+  </si>
+  <si>
+    <t>User stories were generated successfully from the project content</t>
+  </si>
+  <si>
+    <t>Documentation Agent – Risk Register Generation</t>
+  </si>
+  <si>
+    <t>Run the Documentation Generation Agent on a project document containing risks or dependencies</t>
+  </si>
+  <si>
+    <t>Project document contains identifiable risks, dependencies or potential issues</t>
+  </si>
+  <si>
+    <t>A structured risk register is generated</t>
+  </si>
+  <si>
+    <t>Risk register was generated successfully with relevant project risks</t>
+  </si>
+  <si>
+    <t>Documentation Agent – Action Item Generation</t>
+  </si>
+  <si>
+    <t>Run the Documentation Generation Agent on project content containing tasks or pending activities</t>
+  </si>
+  <si>
+    <t>Project document contains tasks, follow-ups, owners or next steps</t>
+  </si>
+  <si>
+    <t>Structured action items are generated</t>
+  </si>
+  <si>
+    <t>Action items were generated successfully from the project evidence</t>
+  </si>
+  <si>
+    <t>Project Health – Overall Score</t>
+  </si>
+  <si>
+    <t>Execute the Project Health Scoring module on a valid project document</t>
+  </si>
+  <si>
+    <t>Project contains sufficient information for health evaluation</t>
+  </si>
+  <si>
+    <t>Overall project health score between 0 and 100 is calculated</t>
+  </si>
+  <si>
+    <t>Overall project health score was calculated successfully</t>
+  </si>
+  <si>
+    <t>Project Health – Dimension-wise Scoring</t>
+  </si>
+  <si>
+    <t>Execute health scoring on a project containing scope, timeline, risks and blockers</t>
+  </si>
+  <si>
+    <t>Required project health dimensions are available</t>
+  </si>
+  <si>
+    <t>Scope clarity, timeline health, risk status and blocker status scores are calculated</t>
+  </si>
+  <si>
+    <t>All four health dimensions were calculated successfully</t>
+  </si>
+  <si>
+    <t>Project Health – Status and Risks</t>
+  </si>
+  <si>
+    <t>Calculate project health for a project containing risks and blockers</t>
+  </si>
+  <si>
+    <t>Project evidence contains identifiable risks and blockers</t>
+  </si>
+  <si>
+    <t>System returns health status along with identified risks and blockers</t>
+  </si>
+  <si>
+    <t>Health status, risks and blockers were returned successfully</t>
+  </si>
+  <si>
+    <t>Conversational Assistant – RAG Question Answering</t>
+  </si>
+  <si>
+    <t>Upload project documents and ask a question whose answer exists in the documents</t>
+  </si>
+  <si>
+    <t>Relevant project evidence is available in the RAG vector store</t>
+  </si>
+  <si>
+    <t>Assistant provides an answer grounded in the uploaded project content</t>
+  </si>
+  <si>
+    <t>Assistant returned a relevant evidence-grounded answer</t>
+  </si>
+  <si>
+    <t>Conversational Assistant – Complete List Retrieval</t>
+  </si>
+  <si>
+    <t>Ask the assistant for complete project deliverables, objectives, responsibilities or features</t>
+  </si>
+  <si>
+    <t>Requested information may span multiple document chunks</t>
+  </si>
+  <si>
+    <t>Assistant retrieves multiple relevant chunks and provides a complete list</t>
+  </si>
+  <si>
+    <t>Relevant chunks were retrieved and the requested list was generated successfully</t>
+  </si>
+  <si>
+    <t>Conversational Assistant – Unsupported Question Handling</t>
+  </si>
+  <si>
+    <t>Ask a question whose answer is not present in the uploaded project documents</t>
+  </si>
+  <si>
+    <t>No relevant evidence exists in the uploaded documents</t>
+  </si>
+  <si>
+    <t>Assistant indicates that sufficient project evidence could not be found</t>
+  </si>
+  <si>
+    <t>Assistant correctly indicated that relevant evidence was unavailable</t>
+  </si>
+  <si>
+    <t>Milestone 3 – End-to-End Validation</t>
+  </si>
+  <si>
+    <t>Upload project documents and execute documentation generation, health scoring and conversational assistant workflows</t>
+  </si>
+  <si>
+    <t>All Milestone 3 modules are integrated and operational</t>
+  </si>
+  <si>
+    <t>Documentation, health insights and evidence-grounded conversational responses are generated successfully</t>
+  </si>
+  <si>
+    <t>End-to-end Milestone 3 workflow executed successfully</t>
   </si>
 </sst>
 </file>
@@ -551,31 +701,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="justify"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -587,8 +725,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,10 +756,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,557 +1055,738 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="118.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="91.28515625" customWidth="1"/>
-    <col min="5" max="5" width="89.42578125" customWidth="1"/>
-    <col min="6" max="6" width="90.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="45" style="10" customWidth="1"/>
+    <col min="3" max="3" width="118.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.28515625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="89.42578125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="90.42578125" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="13" customFormat="1" ht="15.75">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="15.75">
-      <c r="A2" s="9">
+    <row r="2" spans="1:8" s="14" customFormat="1" ht="15.75">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="15.75">
-      <c r="A3" s="9">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75">
-      <c r="A4" s="9">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75">
-      <c r="A5" s="9">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75">
-      <c r="A6" s="9">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75">
-      <c r="A7" s="9">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="7" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75">
-      <c r="A8" s="9">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75">
-      <c r="A9" s="9">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75">
-      <c r="A10" s="9">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75">
-      <c r="A11" s="9">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75">
-      <c r="A12" s="9">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75">
-      <c r="A13" s="9">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75">
-      <c r="A14" s="9">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75">
-      <c r="A15" s="9">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75">
-      <c r="A16" s="9">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>0</v>
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" t="s">
-        <v>85</v>
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
-      <c r="F19" t="s">
-        <v>90</v>
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" t="s">
-        <v>95</v>
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" t="s">
-        <v>100</v>
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="2">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" t="s">
-        <v>105</v>
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" t="s">
-        <v>109</v>
-      </c>
-      <c r="F23" t="s">
-        <v>110</v>
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" t="s">
-        <v>115</v>
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" t="s">
-        <v>120</v>
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" t="s">
-        <v>125</v>
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="2">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" t="s">
-        <v>129</v>
-      </c>
-      <c r="F27" t="s">
-        <v>130</v>
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
